--- a/output/yearly_surface_area_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_19_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626100137</v>
+        <v>10.84497627685262</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907169376703</v>
+        <v>37.78907174900035</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.00829594999048</v>
+        <v>5.37408693304704</v>
       </c>
       <c r="C2" t="n">
-        <v>5.482079180514189</v>
+        <v>6.34994415106837</v>
       </c>
       <c r="D2" t="n">
-        <v>30.86909306463246</v>
+        <v>22.8079626650619</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.03194001035041</v>
+        <v>15.75214191464007</v>
       </c>
       <c r="C3" t="n">
-        <v>17.9758004647591</v>
+        <v>32.84436944557704</v>
       </c>
       <c r="D3" t="n">
-        <v>76.2425267118073</v>
+        <v>53.28926538651687</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.94058072059322</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="C4" t="n">
-        <v>50.52760909447059</v>
+        <v>99.76618345326513</v>
       </c>
       <c r="D4" t="n">
-        <v>94.61004451056087</v>
+        <v>60.22727641242908</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.90237467558562</v>
+        <v>40.44800541496859</v>
       </c>
       <c r="C5" t="n">
-        <v>82.51589454194442</v>
+        <v>151.1646027614026</v>
       </c>
       <c r="D5" t="n">
-        <v>66.97973712223865</v>
+        <v>47.68839473378882</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.94851681768522</v>
+        <v>36.66925850132262</v>
       </c>
       <c r="C6" t="n">
-        <v>100.9109012764169</v>
+        <v>174.9739480847963</v>
       </c>
       <c r="D6" t="n">
-        <v>46.49066253460771</v>
+        <v>39.52712606838509</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.66194429903638</v>
+        <v>24.97271635292611</v>
       </c>
       <c r="C7" t="n">
-        <v>89.29093544895164</v>
+        <v>185.4688310431947</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>37.54890444432775</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.43936530761284</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>51.07051557491908</v>
+        <v>126.1742149498001</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>34.96494448675015</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>63.01249464937726</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.713826171840252</v>
+        <v>7.639672420316604</v>
       </c>
       <c r="C21" t="n">
-        <v>96.42282714800317</v>
+        <v>91.67606904379925</v>
       </c>
       <c r="D21" t="n">
-        <v>8.678054443320285</v>
+        <v>7.639672420316604</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.739697989654353</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C2" t="n">
-        <v>9.562222639363933</v>
+        <v>6.860452957276711</v>
       </c>
       <c r="D2" t="n">
-        <v>31.67216268670635</v>
+        <v>18.87311786644068</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.11815388187489</v>
+        <v>16.56699250916493</v>
       </c>
       <c r="C3" t="n">
-        <v>19.68404147014855</v>
+        <v>28.64739800992193</v>
       </c>
       <c r="D3" t="n">
-        <v>82.24100518475531</v>
+        <v>57.56477663851173</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.53668150352029</v>
+        <v>30.82196917482861</v>
       </c>
       <c r="C4" t="n">
-        <v>47.57942073861742</v>
+        <v>91.20239822912019</v>
       </c>
       <c r="D4" t="n">
-        <v>109.6317661332413</v>
+        <v>70.4246898164407</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.04396732917541</v>
+        <v>44.20319038371264</v>
       </c>
       <c r="C5" t="n">
-        <v>87.03193398147975</v>
+        <v>164.1482161500667</v>
       </c>
       <c r="D5" t="n">
-        <v>83.05585577928017</v>
+        <v>55.59146375297565</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.83784136901259</v>
+        <v>44.07556318216056</v>
       </c>
       <c r="C6" t="n">
-        <v>116.0455238850857</v>
+        <v>202.4255773909456</v>
       </c>
       <c r="D6" t="n">
-        <v>56.19131160027045</v>
+        <v>44.55858305264999</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.54323494228053</v>
+        <v>32.81786225756237</v>
       </c>
       <c r="C7" t="n">
-        <v>116.3596831504447</v>
+        <v>216.9093012716988</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.70077223884975</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="C8" t="n">
-        <v>84.11614329986671</v>
+        <v>177.9957675184679</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.98124898262807</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59374604355361</v>
+        <v>103.9484286733565</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>50.53546307610457</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.903004700764742</v>
+        <v>7.806074160448412</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7026878727284</v>
+        <v>99.52744554571724</v>
       </c>
       <c r="D21" t="n">
-        <v>9.878755875955928</v>
+        <v>8.781833430504463</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.432811868852601</v>
+        <v>8.399833357535709</v>
       </c>
       <c r="C2" t="n">
-        <v>9.168541809960962</v>
+        <v>9.607383033759286</v>
       </c>
       <c r="D2" t="n">
-        <v>25.89850443803086</v>
+        <v>28.62874480354123</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.04237938219863</v>
+        <v>17.67636741496382</v>
       </c>
       <c r="C3" t="n">
-        <v>28.18106785040469</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D3" t="n">
-        <v>86.58523877604745</v>
+        <v>58.09001166028377</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.71085175779947</v>
+        <v>30.17107044691297</v>
       </c>
       <c r="C4" t="n">
-        <v>48.24308218668826</v>
+        <v>81.68140899333463</v>
       </c>
       <c r="D4" t="n">
-        <v>121.2458414744811</v>
+        <v>78.24823727158353</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.43666641087414</v>
+        <v>44.52225838759286</v>
       </c>
       <c r="C5" t="n">
-        <v>86.34471058850698</v>
+        <v>163.5591675275186</v>
       </c>
       <c r="D5" t="n">
-        <v>100.1382658331747</v>
+        <v>64.08358139471056</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.8692983532775</v>
+        <v>49.79129831628549</v>
       </c>
       <c r="C6" t="n">
-        <v>126.4707027564826</v>
+        <v>224.3627298423406</v>
       </c>
       <c r="D6" t="n">
-        <v>66.41523219229674</v>
+        <v>50.2340665309008</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.46633982617978</v>
+        <v>40.3036885024443</v>
       </c>
       <c r="C7" t="n">
-        <v>138.8770484950495</v>
+        <v>249.0085242097525</v>
       </c>
       <c r="D7" t="n">
-        <v>48.92736033654828</v>
+        <v>42.27994663109313</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.54631905411351</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="C8" t="n">
-        <v>115.3259028178728</v>
+        <v>221.222118936455</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.52812351162255</v>
+        <v>12.97968639784708</v>
       </c>
       <c r="C9" t="n">
-        <v>72.77499382040753</v>
+        <v>149.654674792271</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>43.13308538608361</v>
+        <v>78.86379308214629</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>35.53926689373453</v>
+        <v>42.29172760354408</v>
       </c>
       <c r="D11" t="n">
-        <v>37.49392657288993</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
         <v>35.36549755008285</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>32.00006641992479</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.077465329410487</v>
+        <v>7.95638969279335</v>
       </c>
       <c r="C21" t="n">
-        <v>114.0941977779231</v>
+        <v>106.416712141111</v>
       </c>
       <c r="D21" t="n">
-        <v>11.10651482793942</v>
+        <v>9.945487115991687</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.740679737358599</v>
+        <v>7.568293052038661</v>
       </c>
       <c r="C2" t="n">
-        <v>6.08781751403447</v>
+        <v>6.763259934556276</v>
       </c>
       <c r="D2" t="n">
-        <v>21.1762979806037</v>
+        <v>23.57176237896592</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.86628669023996</v>
+        <v>20.7296027751714</v>
       </c>
       <c r="C3" t="n">
-        <v>40.40873550679871</v>
+        <v>44.85605260703677</v>
       </c>
       <c r="D3" t="n">
-        <v>94.70920102868979</v>
+        <v>61.95318887649498</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.30923483130452</v>
+        <v>21.3903189801295</v>
       </c>
       <c r="C4" t="n">
-        <v>70.8841477420282</v>
+        <v>123.9898263078509</v>
       </c>
       <c r="D4" t="n">
-        <v>115.796159968207</v>
+        <v>73.67918345601888</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.46501392111028</v>
+        <v>28.02889695624644</v>
       </c>
       <c r="C5" t="n">
-        <v>75.57002953439824</v>
+        <v>134.057649014902</v>
       </c>
       <c r="D5" t="n">
-        <v>67.54424205218056</v>
+        <v>46.60847225911733</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.71201343195298</v>
+        <v>24.99627829782805</v>
       </c>
       <c r="C6" t="n">
-        <v>91.4517621459989</v>
+        <v>163.9852460311618</v>
       </c>
       <c r="D6" t="n">
-        <v>32.20132469929539</v>
+        <v>27.81389420901639</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>81.08646988456105</v>
+        <v>155.525526063667</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>53.57397222074844</v>
+        <v>110.3189895262141</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>60.12811989430013</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>28.25371718051895</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.100760160638926</v>
+        <v>4.401174958138451</v>
       </c>
       <c r="C2" t="n">
-        <v>2.596722677732814</v>
+        <v>3.295727043156542</v>
       </c>
       <c r="D2" t="n">
-        <v>14.44249047717483</v>
+        <v>16.49434317905066</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.33752558827843</v>
+        <v>23.51285751671111</v>
       </c>
       <c r="C3" t="n">
-        <v>32.29949946972006</v>
+        <v>36.50628838241764</v>
       </c>
       <c r="D3" t="n">
-        <v>91.61669576031234</v>
+        <v>65.63965150594174</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.9022925601276</v>
+        <v>28.71612034921921</v>
       </c>
       <c r="C4" t="n">
-        <v>87.84580282830034</v>
+        <v>121.7180621202238</v>
       </c>
       <c r="D4" t="n">
-        <v>133.42147650255</v>
+        <v>85.43364871896593</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.55751918948773</v>
+        <v>30.85142160595602</v>
       </c>
       <c r="C5" t="n">
-        <v>103.8443634167064</v>
+        <v>178.7762569433442</v>
       </c>
       <c r="D5" t="n">
-        <v>88.28366230439444</v>
+        <v>57.0395416167397</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.87051678069322</v>
+        <v>29.5044637557294</v>
       </c>
       <c r="C6" t="n">
-        <v>108.8404774836184</v>
+        <v>192.2821601106676</v>
       </c>
       <c r="D6" t="n">
-        <v>40.29190752999335</v>
+        <v>32.48308629041422</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>15.51063197939536</v>
       </c>
       <c r="C7" t="n">
-        <v>103.0049691295753</v>
+        <v>189.3015740805742</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>29.70375853969149</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>72.34989706446869</v>
+        <v>142.8639259219958</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>39.38280915586078</v>
+        <v>62.56874468705769</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>62.58837964114266</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.373105185342792</v>
+        <v>3.878885179479147</v>
       </c>
       <c r="C2" t="n">
-        <v>8.24275372485622</v>
+        <v>8.334056261351174</v>
       </c>
       <c r="D2" t="n">
-        <v>13.81220845104838</v>
+        <v>15.32802690640545</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03608798534566</v>
+        <v>19.23734626471625</v>
       </c>
       <c r="C3" t="n">
-        <v>20.17982406079319</v>
+        <v>24.46024405130928</v>
       </c>
       <c r="D3" t="n">
-        <v>82.51589454194442</v>
+        <v>64.14739499548659</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.99836496642355</v>
+        <v>36.24612524079224</v>
       </c>
       <c r="C4" t="n">
-        <v>84.0425122220482</v>
+        <v>106.5687132959913</v>
       </c>
       <c r="D4" t="n">
-        <v>147.4604686732794</v>
+        <v>95.0950278764588</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.67519004527711</v>
+        <v>36.20194659410114</v>
       </c>
       <c r="C5" t="n">
-        <v>133.5422314701724</v>
+        <v>200.0065510476815</v>
       </c>
       <c r="D5" t="n">
-        <v>113.0482481440202</v>
+        <v>71.76575718044185</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.82147045320988</v>
+        <v>34.69692736349078</v>
       </c>
       <c r="C6" t="n">
-        <v>137.7009147453619</v>
+        <v>235.9149550782128</v>
       </c>
       <c r="D6" t="n">
-        <v>55.78879504152925</v>
+        <v>40.8151790563569</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.78171751895449</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="C7" t="n">
-        <v>130.4929231007818</v>
+        <v>230.8628813921587</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>102.9755166984479</v>
+        <v>190.3461536378928</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>62.01405723415825</v>
+        <v>108.0531158248124</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>38.86248287260999</v>
+        <v>49.82369599052563</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.100359250011427</v>
+        <v>2.338523031515902</v>
       </c>
       <c r="C2" t="n">
-        <v>3.73064127613788</v>
+        <v>4.07228947721577</v>
       </c>
       <c r="D2" t="n">
-        <v>9.529824965123789</v>
+        <v>10.70301347169872</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2829075697391</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="C3" t="n">
-        <v>26.90479583488384</v>
+        <v>29.30026023324605</v>
       </c>
       <c r="D3" t="n">
-        <v>79.02578145334701</v>
+        <v>64.00504157837081</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.42702886028091</v>
+        <v>39.81968688425063</v>
       </c>
       <c r="C4" t="n">
-        <v>79.44793296617313</v>
+        <v>101.3742861928214</v>
       </c>
       <c r="D4" t="n">
-        <v>156.4837118230118</v>
+        <v>103.6715758207589</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.27682146153116</v>
+        <v>37.42913122440965</v>
       </c>
       <c r="C5" t="n">
-        <v>157.6441376094316</v>
+        <v>236.8711773421492</v>
       </c>
       <c r="D5" t="n">
-        <v>122.7430067234575</v>
+        <v>75.69274799742909</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.87051678069322</v>
+        <v>27.73339089726815</v>
       </c>
       <c r="C6" t="n">
-        <v>173.4846368174539</v>
+        <v>273.8320149116332</v>
       </c>
       <c r="D6" t="n">
-        <v>54.74225198880216</v>
+        <v>40.45291415348983</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.941177253203202</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>138.0386359556228</v>
+        <v>244.3373686329462</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>78.94233289848603</v>
+        <v>133.6845848872882</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>19.01350778814797</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.38973814305275</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.14257440129404</v>
+        <v>2.368957210347553</v>
       </c>
       <c r="C2" t="n">
-        <v>8.163232160812228</v>
+        <v>11.09178556258046</v>
       </c>
       <c r="D2" t="n">
-        <v>16.12716953766235</v>
+        <v>15.52633994266331</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.52633994266331</v>
+        <v>13.56775327269092</v>
       </c>
       <c r="C3" t="n">
-        <v>20.41544350981242</v>
+        <v>22.44275251908209</v>
       </c>
       <c r="D3" t="n">
-        <v>69.8268054645544</v>
+        <v>58.46307578789757</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.25736643389546</v>
+        <v>38.04566878267665</v>
       </c>
       <c r="C4" t="n">
-        <v>73.14314920950011</v>
+        <v>88.62432875776805</v>
       </c>
       <c r="D4" t="n">
-        <v>159.7126800222796</v>
+        <v>110.1550376596049</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.33973543006097</v>
+        <v>46.38757902566179</v>
       </c>
       <c r="C5" t="n">
-        <v>153.5698846368073</v>
+        <v>216.1072133973292</v>
       </c>
       <c r="D5" t="n">
-        <v>146.3785827031994</v>
+        <v>91.17981803192252</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.32965591111124</v>
+        <v>35.94472869558847</v>
       </c>
       <c r="C6" t="n">
-        <v>212.7702529505943</v>
+        <v>320.3226774462408</v>
       </c>
       <c r="D6" t="n">
-        <v>75.63286138747003</v>
+        <v>51.56237117474674</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.73883941513712</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>188.7027079809837</v>
+        <v>311.3504851771292</v>
       </c>
       <c r="D7" t="n">
-        <v>40.78278138211675</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>124.5052438525805</v>
+        <v>207.1193131649496</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>55.24687030878498</v>
+        <v>81.53905557621881</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.56913593102267</v>
+      </c>
+      <c r="D13" t="n">
         <v>16.1301147807751</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.356194490192345</v>
+        <v>1.64050041379642</v>
       </c>
       <c r="C2" t="n">
-        <v>4.50327671938012</v>
+        <v>6.939974521320702</v>
       </c>
       <c r="D2" t="n">
-        <v>12.74504869653209</v>
+        <v>11.29206209424681</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.64629308903066</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="C3" t="n">
-        <v>26.32065595085699</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="D3" t="n">
-        <v>67.96639356500668</v>
+        <v>57.52059799182062</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.36473678655685</v>
+        <v>34.01264921363074</v>
       </c>
       <c r="C4" t="n">
-        <v>65.24302543342603</v>
+        <v>76.8571007746658</v>
       </c>
       <c r="D4" t="n">
-        <v>159.3170356974681</v>
+        <v>113.0777005751476</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.78843518863076</v>
+        <v>51.22268646907735</v>
       </c>
       <c r="C5" t="n">
-        <v>149.9619618237003</v>
+        <v>204.1053477129119</v>
       </c>
       <c r="D5" t="n">
-        <v>163.2400995236384</v>
+        <v>102.8871594050658</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.42023874180921</v>
+        <v>41.78121879733577</v>
       </c>
       <c r="C6" t="n">
-        <v>234.3853921549963</v>
+        <v>343.7491411649783</v>
       </c>
       <c r="D6" t="n">
-        <v>90.4052190932718</v>
+        <v>59.4516957260741</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>235.3543771390878</v>
+        <v>369.7998164971673</v>
       </c>
       <c r="D7" t="n">
-        <v>46.23246288839079</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>162.2239906497429</v>
+        <v>259.9422483919492</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>66.89530681967339</v>
+        <v>88.86092995449152</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
         <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.44775906859456</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.239186586937727</v>
+        <v>2.411172361630166</v>
       </c>
       <c r="C2" t="n">
-        <v>4.78012957197772</v>
+        <v>8.170104394741955</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17014545247096</v>
+        <v>17.53695924096077</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.90230825566083</v>
+        <v>8.732645829275379</v>
       </c>
       <c r="C3" t="n">
-        <v>22.10895829963817</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D3" t="n">
-        <v>62.96438901186919</v>
+        <v>53.80959166976768</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.43007191438489</v>
+        <v>28.32047602440774</v>
       </c>
       <c r="C4" t="n">
-        <v>65.29407631404686</v>
+        <v>77.81430478630644</v>
       </c>
       <c r="D4" t="n">
-        <v>157.1346105509275</v>
+        <v>114.5326506728414</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.00303702523332</v>
+        <v>51.41903600992671</v>
       </c>
       <c r="C5" t="n">
-        <v>136.4874745829128</v>
+        <v>178.2362957060084</v>
       </c>
       <c r="D5" t="n">
-        <v>178.8744317137689</v>
+        <v>113.0482481440202</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.0869275484508</v>
+        <v>50.67683474551611</v>
       </c>
       <c r="C6" t="n">
-        <v>236.9614981309399</v>
+        <v>337.6711411279863</v>
       </c>
       <c r="D6" t="n">
-        <v>113.0266496945268</v>
+        <v>72.29197394991814</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.59071868498287</v>
+        <v>25.09248957284423</v>
       </c>
       <c r="C7" t="n">
-        <v>281.946159687233</v>
+        <v>419.5655893731424</v>
       </c>
       <c r="D7" t="n">
-        <v>56.95216607106171</v>
+        <v>44.01665831990574</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>222.2235015947867</v>
+        <v>347.3963338862551</v>
       </c>
       <c r="D8" t="n">
-        <v>39.05392367493811</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>118.481239939322</v>
+        <v>166.739048341574</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>49.53898915629405</v>
+        <v>55.94489292650449</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.770713005562751</v>
+        <v>4.061490252469055</v>
       </c>
       <c r="C2" t="n">
-        <v>2.821542902005333</v>
+        <v>17.50063457590364</v>
       </c>
       <c r="D2" t="n">
-        <v>7.249225048158447</v>
+        <v>7.025386571590175</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.999239236474005</v>
+        <v>1.761255381418778</v>
       </c>
       <c r="C2" t="n">
-        <v>2.676244241776805</v>
+        <v>4.836089191119788</v>
       </c>
       <c r="D2" t="n">
-        <v>9.693776831733006</v>
+        <v>13.04840873714436</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.14836707652828</v>
+        <v>11.92332586807751</v>
       </c>
       <c r="C3" t="n">
-        <v>24.41115666609694</v>
+        <v>35.0582105186536</v>
       </c>
       <c r="D3" t="n">
-        <v>68.13819941324986</v>
+        <v>59.95042355983148</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.89924950602363</v>
+        <v>39.168788156335</v>
       </c>
       <c r="C4" t="n">
-        <v>90.42387229965247</v>
+        <v>111.0356653503143</v>
       </c>
       <c r="D4" t="n">
-        <v>163.2224280649619</v>
+        <v>115.2601257216883</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.82812170296135</v>
+        <v>29.01064466049325</v>
       </c>
       <c r="C5" t="n">
-        <v>200.8410365962913</v>
+        <v>276.6565030567512</v>
       </c>
       <c r="D5" t="n">
-        <v>164.2709346130976</v>
+        <v>103.4025769497953</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.70193391300324</v>
+        <v>15.57739082328414</v>
       </c>
       <c r="C6" t="n">
-        <v>236.8004915074434</v>
+        <v>335.900068269525</v>
       </c>
       <c r="D6" t="n">
-        <v>87.62785483795757</v>
+        <v>60.21647718768238</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>4.611268966847268</v>
       </c>
       <c r="C7" t="n">
-        <v>156.2441653831756</v>
+        <v>244.2774820229871</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>29.88341836956866</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>87.2871883845839</v>
+        <v>122.8362727553609</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>23.94973524510094</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82968428774233</v>
+        <v>42.71093387325747</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.20360698987336</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>18.50594422505238</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.23654444346124</v>
+        <v>14.74879576089983</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.53116656572653</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.803511590430396</v>
+        <v>7.361144286442584</v>
       </c>
       <c r="C2" t="n">
-        <v>4.215624642035804</v>
+        <v>8.464628706015999</v>
       </c>
       <c r="D2" t="n">
-        <v>15.13854959948582</v>
+        <v>10.41241615124167</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.25712008752143</v>
+        <v>8.634471058850698</v>
       </c>
       <c r="C3" t="n">
-        <v>7.220754364735291</v>
+        <v>44.10010687476672</v>
       </c>
       <c r="D3" t="n">
-        <v>9.513135254151592</v>
+        <v>9.036987617591889</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39928429591006</v>
+        <v>13.39709530583433</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14919425505856</v>
+        <v>70.13773424819152</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576386387754125</v>
+        <v>1.576128859509922</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.124723016168351</v>
+        <v>4.661338099763856</v>
       </c>
       <c r="C2" t="n">
-        <v>8.421431807029139</v>
+        <v>9.069385291832035</v>
       </c>
       <c r="D2" t="n">
-        <v>20.76887268334128</v>
+        <v>13.64531134132642</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.99190933865455</v>
+        <v>18.61884521104076</v>
       </c>
       <c r="C3" t="n">
-        <v>13.08669689760998</v>
+        <v>37.16405934426301</v>
       </c>
       <c r="D3" t="n">
-        <v>19.92947839621025</v>
+        <v>15.59997102048182</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.26872113352314</v>
+        <v>10.18465068385641</v>
       </c>
       <c r="C4" t="n">
-        <v>11.72893982263664</v>
+        <v>67.7317558636917</v>
       </c>
       <c r="D4" t="n">
-        <v>20.05023336383261</v>
+        <v>19.80774168088364</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44517923660203</v>
+        <v>15.43649389349136</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16784205683238</v>
+        <v>86.11938698474128</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251616681389901</v>
+        <v>3.249788188103444</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.642684893383167</v>
+        <v>4.407065444363932</v>
       </c>
       <c r="C2" t="n">
-        <v>5.411393345808419</v>
+        <v>8.447938995043803</v>
       </c>
       <c r="D2" t="n">
-        <v>23.93500902953724</v>
+        <v>11.22530325035803</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.29486846863931</v>
+        <v>17.19531103988288</v>
       </c>
       <c r="C3" t="n">
-        <v>25.0247489812512</v>
+        <v>36.0252320073367</v>
       </c>
       <c r="D3" t="n">
-        <v>31.9166178650638</v>
+        <v>22.89435646303562</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.92933952749001</v>
+        <v>24.38955821660351</v>
       </c>
       <c r="C4" t="n">
-        <v>23.99391389179205</v>
+        <v>82.40888404218151</v>
       </c>
       <c r="D4" t="n">
-        <v>25.53820303057228</v>
+        <v>23.18986252201391</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.73817646260237</v>
+        <v>9.40023426816321</v>
       </c>
       <c r="C5" t="n">
-        <v>14.82439033412684</v>
+        <v>72.40389318820228</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>30.09056713516474</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,7 +5361,7 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74337499084588</v>
+        <v>16.72182609863513</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1345874441599</v>
+        <v>101.1670478967425</v>
       </c>
       <c r="D21" t="n">
-        <v>5.023012497253764</v>
+        <v>4.180456524658783</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.075635630956009</v>
+        <v>5.022621254926682</v>
       </c>
       <c r="C2" t="n">
-        <v>3.496985322527138</v>
+        <v>4.962734644967626</v>
       </c>
       <c r="D2" t="n">
-        <v>29.04009709162065</v>
+        <v>17.61451730959627</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98914402199105</v>
+        <v>16.01721379478671</v>
       </c>
       <c r="C3" t="n">
-        <v>22.66364575253762</v>
+        <v>34.14518515370406</v>
       </c>
       <c r="D3" t="n">
-        <v>43.00545818453153</v>
+        <v>26.33047342789946</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.43457974227862</v>
+        <v>29.15005283449629</v>
       </c>
       <c r="C4" t="n">
-        <v>45.95855527890593</v>
+        <v>86.63334441355555</v>
       </c>
       <c r="D4" t="n">
-        <v>34.98261594542659</v>
+        <v>29.11176467403067</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.87534340375644</v>
+        <v>22.5311098124643</v>
       </c>
       <c r="C5" t="n">
-        <v>31.04777114680538</v>
+        <v>113.9809084630547</v>
       </c>
       <c r="D5" t="n">
-        <v>32.2749557771139</v>
+        <v>31.66136346195964</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55222523587222</v>
+        <v>9.338384162795663</v>
       </c>
       <c r="C6" t="n">
-        <v>18.07299348747954</v>
+        <v>65.32843748369551</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>37.39378830705677</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.83593462686631</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.46575898910303</v>
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07625504064653</v>
+        <v>18.03425764232279</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9260447889798</v>
+        <v>116.7932875883762</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886192396436774</v>
+        <v>6.011419214107597</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.428083056780614</v>
+        <v>6.215444715586557</v>
       </c>
       <c r="C2" t="n">
-        <v>6.33129094468768</v>
+        <v>16.88998750386213</v>
       </c>
       <c r="D2" t="n">
-        <v>24.94915440802419</v>
+        <v>19.24520024635022</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.39871274111122</v>
+        <v>14.76548547187203</v>
       </c>
       <c r="C3" t="n">
-        <v>16.34119053718816</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D3" t="n">
-        <v>52.21916038888784</v>
+        <v>31.39138284329177</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.623795007291</v>
+        <v>21.86253962587222</v>
       </c>
       <c r="C4" t="n">
-        <v>43.64850293081319</v>
+        <v>71.06282582420111</v>
       </c>
       <c r="D4" t="n">
-        <v>41.54265410520378</v>
+        <v>30.24764676784423</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.75200304591983</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="C5" t="n">
-        <v>44.74315162104839</v>
+        <v>102.5680914011855</v>
       </c>
       <c r="D5" t="n">
-        <v>30.53235360207581</v>
+        <v>28.24979018970198</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.20254312671111</v>
+        <v>10.6666888066416</v>
       </c>
       <c r="C6" t="n">
-        <v>23.54721868635975</v>
+        <v>83.20017269180445</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>29.94723197034471</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>15.39085875947725</v>
+        <v>36.77037851486003</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.067957860467356</v>
+        <v>7.041901468375008</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14559967443988</v>
+        <v>66.0178262660157</v>
       </c>
       <c r="D21" t="n">
-        <v>5.300968395350517</v>
+        <v>4.40118841773438</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.873395603881167</v>
+        <v>4.98040610364407</v>
       </c>
       <c r="C2" t="n">
-        <v>4.995132319207771</v>
+        <v>8.278096642209105</v>
       </c>
       <c r="D2" t="n">
-        <v>31.65449122802991</v>
+        <v>22.82072538521711</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.75490723130357</v>
+        <v>18.83973844449629</v>
       </c>
       <c r="C3" t="n">
-        <v>21.95187866695868</v>
+        <v>50.73181261695393</v>
       </c>
       <c r="D3" t="n">
-        <v>61.05488972710914</v>
+        <v>39.97185777840889</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.07798434145878</v>
+        <v>25.98489823600458</v>
       </c>
       <c r="C4" t="n">
-        <v>42.0148747509465</v>
+        <v>64.80909294814894</v>
       </c>
       <c r="D4" t="n">
-        <v>60.17622553180824</v>
+        <v>39.67929696254333</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.63052837250049</v>
+        <v>27.4889357189107</v>
       </c>
       <c r="C5" t="n">
-        <v>67.49515466696822</v>
+        <v>120.0677442293849</v>
       </c>
       <c r="D5" t="n">
-        <v>39.24536447726625</v>
+        <v>32.86400439966199</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.42646371873739</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="C6" t="n">
-        <v>52.40765594810324</v>
+        <v>129.5298286029157</v>
       </c>
       <c r="D6" t="n">
-        <v>34.13340418125311</v>
+        <v>32.6440929139107</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.67788894201581</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>26.70942804173872</v>
+        <v>84.5000066522272</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>20.11110172149591</v>
+        <v>35.71598148049896</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>22.85312305945724</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295211439148613</v>
+        <v>7.256890386090404</v>
       </c>
       <c r="C21" t="n">
-        <v>77.51162154095401</v>
+        <v>75.29023775568795</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383310009255037</v>
+        <v>5.442667789567803</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.372704274715294</v>
+        <v>4.11548637620263</v>
       </c>
       <c r="C2" t="n">
-        <v>4.176354733865931</v>
+        <v>6.864379948093698</v>
       </c>
       <c r="D2" t="n">
-        <v>26.4404291707751</v>
+        <v>20.42526098685489</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.30821202587127</v>
+        <v>17.86780821729195</v>
       </c>
       <c r="C3" t="n">
-        <v>20.41544350981242</v>
+        <v>40.30074325933157</v>
       </c>
       <c r="D3" t="n">
-        <v>72.21245238587413</v>
+        <v>48.42470551197393</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.8557495074005</v>
+        <v>31.56220694383071</v>
       </c>
       <c r="C4" t="n">
-        <v>49.81289676577891</v>
+        <v>98.89831848271095</v>
       </c>
       <c r="D4" t="n">
-        <v>76.6911854126481</v>
+        <v>49.8001340456237</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.52730599483434</v>
+        <v>33.79666471869646</v>
       </c>
       <c r="C5" t="n">
-        <v>72.84567965511334</v>
+        <v>119.9695694589603</v>
       </c>
       <c r="D5" t="n">
-        <v>52.71985171805373</v>
+        <v>39.785325714602</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.48937768726721</v>
+        <v>28.73968229412113</v>
       </c>
       <c r="C6" t="n">
-        <v>83.64294090641977</v>
+        <v>162.375179796197</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>35.86422538384024</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.84054026575129</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>54.31715523286327</v>
+        <v>137.6793162958684</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>28.95664853675967</v>
+        <v>75.8547363686298</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>24.73906039931537</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.510709187282086</v>
+        <v>7.456439697630374</v>
       </c>
       <c r="C21" t="n">
-        <v>87.31199430215425</v>
+        <v>83.88494659834171</v>
       </c>
       <c r="D21" t="n">
-        <v>7.510709187282086</v>
+        <v>6.524384735426578</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_19_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497627685262</v>
+        <v>10.84497620096166</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907174900035</v>
+        <v>37.78907148456001</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.37408693304704</v>
+        <v>6.099598486485433</v>
       </c>
       <c r="C2" t="n">
-        <v>6.34994415106837</v>
+        <v>5.079562621772997</v>
       </c>
       <c r="D2" t="n">
-        <v>22.8079626650619</v>
+        <v>24.97958858685584</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.75214191464007</v>
+        <v>19.89511722656161</v>
       </c>
       <c r="C3" t="n">
-        <v>32.84436944557704</v>
+        <v>25.88377822246716</v>
       </c>
       <c r="D3" t="n">
-        <v>53.28926538651687</v>
+        <v>85.08316478854982</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.6087499965578</v>
+        <v>39.36022895866312</v>
       </c>
       <c r="C4" t="n">
-        <v>99.76618345326513</v>
+        <v>82.3961213220263</v>
       </c>
       <c r="D4" t="n">
-        <v>60.22727641242908</v>
+        <v>100.0724887369901</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.44800541496859</v>
+        <v>51.17359908386501</v>
       </c>
       <c r="C5" t="n">
-        <v>151.1646027614026</v>
+        <v>124.1665408946154</v>
       </c>
       <c r="D5" t="n">
-        <v>47.68839473378882</v>
+        <v>75.07915568227483</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.66925850132262</v>
+        <v>48.06047711369836</v>
       </c>
       <c r="C6" t="n">
-        <v>174.9739480847963</v>
+        <v>111.0945702125691</v>
       </c>
       <c r="D6" t="n">
-        <v>39.52712606838509</v>
+        <v>50.79758971313847</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.97271635292611</v>
+        <v>33.41672835715293</v>
       </c>
       <c r="C7" t="n">
-        <v>185.4688310431947</v>
+        <v>72.58257127037518</v>
       </c>
       <c r="D7" t="n">
-        <v>37.54890444432775</v>
+        <v>40.8426679920758</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>17.60764507566654</v>
       </c>
       <c r="C8" t="n">
-        <v>126.1742149498001</v>
+        <v>41.39048321104552</v>
       </c>
       <c r="D8" t="n">
-        <v>34.96494448675015</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>63.01249464937726</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
         <v>34.59188035913637</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.639672420316604</v>
+        <v>7.693734879940873</v>
       </c>
       <c r="C21" t="n">
-        <v>91.67606904379925</v>
+        <v>94.24825227927569</v>
       </c>
       <c r="D21" t="n">
-        <v>7.639672420316604</v>
+        <v>8.655451739933483</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.075054793879263</v>
+        <v>9.157742585214248</v>
       </c>
       <c r="C2" t="n">
-        <v>6.860452957276711</v>
+        <v>6.211517724769569</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87311786644068</v>
+        <v>25.93973784160922</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56699250916493</v>
+        <v>20.07674055184727</v>
       </c>
       <c r="C3" t="n">
-        <v>28.64739800992193</v>
+        <v>22.58019719767664</v>
       </c>
       <c r="D3" t="n">
-        <v>57.56477663851173</v>
+        <v>84.77882300023332</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.82196917482861</v>
+        <v>38.61999118966102</v>
       </c>
       <c r="C4" t="n">
-        <v>91.20239822912019</v>
+        <v>73.4239290529147</v>
       </c>
       <c r="D4" t="n">
-        <v>70.4246898164407</v>
+        <v>116.7916521403133</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.20319038371264</v>
+        <v>54.63425974133501</v>
       </c>
       <c r="C5" t="n">
-        <v>164.1482161500667</v>
+        <v>136.1684065790326</v>
       </c>
       <c r="D5" t="n">
-        <v>55.59146375297565</v>
+        <v>90.09989555725103</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.07556318216056</v>
+        <v>57.7611261793611</v>
       </c>
       <c r="C6" t="n">
-        <v>202.4255773909456</v>
+        <v>151.7487426454295</v>
       </c>
       <c r="D6" t="n">
-        <v>44.55858305264999</v>
+        <v>61.22276858453534</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.81786225756237</v>
+        <v>44.85507085933252</v>
       </c>
       <c r="C7" t="n">
-        <v>216.9093012716988</v>
+        <v>112.7065999429423</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>45.09461729916874</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.77592484372025</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C8" t="n">
-        <v>177.9957675184679</v>
+        <v>67.09263810822702</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>12.53593643552752</v>
       </c>
       <c r="C9" t="n">
-        <v>103.9484286733565</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>50.53546307610457</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
         <v>32.5203927031756</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.806074160448412</v>
+        <v>7.874105827757782</v>
       </c>
       <c r="C21" t="n">
-        <v>99.52744554571724</v>
+        <v>102.3633757608512</v>
       </c>
       <c r="D21" t="n">
-        <v>8.781833430504463</v>
+        <v>9.842632284697226</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.399833357535709</v>
+        <v>12.17858027118168</v>
       </c>
       <c r="C2" t="n">
-        <v>9.607383033759286</v>
+        <v>6.092726252555705</v>
       </c>
       <c r="D2" t="n">
-        <v>28.62874480354123</v>
+        <v>24.72237068834318</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.67636741496382</v>
+        <v>24.52405765208533</v>
       </c>
       <c r="C3" t="n">
-        <v>27.47420950334699</v>
+        <v>23.12997591205485</v>
       </c>
       <c r="D3" t="n">
-        <v>58.09001166028377</v>
+        <v>85.78020565856507</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.17107044691297</v>
+        <v>37.62449901755476</v>
       </c>
       <c r="C4" t="n">
-        <v>81.68140899333463</v>
+        <v>65.39617807528853</v>
       </c>
       <c r="D4" t="n">
-        <v>78.24823727158353</v>
+        <v>127.0401164249458</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.52225838759286</v>
+        <v>55.7141822160065</v>
       </c>
       <c r="C5" t="n">
-        <v>163.5591675275186</v>
+        <v>134.1312800927205</v>
       </c>
       <c r="D5" t="n">
-        <v>64.08358139471056</v>
+        <v>105.8569462104124</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.79129831628549</v>
+        <v>65.00642423670256</v>
       </c>
       <c r="C6" t="n">
-        <v>224.3627298423406</v>
+        <v>179.924901757313</v>
       </c>
       <c r="D6" t="n">
-        <v>50.2340665309008</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.3036885024443</v>
+        <v>54.73636150257666</v>
       </c>
       <c r="C7" t="n">
-        <v>249.0085242097525</v>
+        <v>156.9628047026843</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>50.48441219548373</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.20146356801562</v>
+        <v>35.38218726105504</v>
       </c>
       <c r="C8" t="n">
-        <v>221.222118936455</v>
+        <v>101.6403398206723</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.97968639784708</v>
+        <v>18.19374845510188</v>
       </c>
       <c r="C9" t="n">
-        <v>149.654674792271</v>
+        <v>58.242182554442</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>78.86379308214629</v>
+        <v>38.29306920414684</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>42.29172760354408</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>27.27884171020187</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.95638969279335</v>
+        <v>8.038779218519894</v>
       </c>
       <c r="C21" t="n">
-        <v>106.416712141111</v>
+        <v>110.5332142546485</v>
       </c>
       <c r="D21" t="n">
-        <v>9.945487115991687</v>
+        <v>11.05332142546485</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.568293052038661</v>
+        <v>10.79824299901067</v>
       </c>
       <c r="C2" t="n">
-        <v>6.763259934556276</v>
+        <v>4.142975311921539</v>
       </c>
       <c r="D2" t="n">
-        <v>23.57176237896592</v>
+        <v>20.43606021160161</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.7296027751714</v>
+        <v>27.99944452511903</v>
       </c>
       <c r="C3" t="n">
-        <v>44.85605260703677</v>
+        <v>36.00068831473054</v>
       </c>
       <c r="D3" t="n">
-        <v>61.95318887649498</v>
+        <v>94.06124754388691</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.3903189801295</v>
+        <v>26.7634241654723</v>
       </c>
       <c r="C4" t="n">
-        <v>123.9898263078509</v>
+        <v>103.3652705370339</v>
       </c>
       <c r="D4" t="n">
-        <v>73.67918345601888</v>
+        <v>120.9778243512217</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.02889695624644</v>
+        <v>36.61918936840603</v>
       </c>
       <c r="C5" t="n">
-        <v>134.057649014902</v>
+        <v>107.5013736150258</v>
       </c>
       <c r="D5" t="n">
-        <v>46.60847225911733</v>
+        <v>71.98665041389738</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.99627829782805</v>
+        <v>33.97239755775664</v>
       </c>
       <c r="C6" t="n">
-        <v>163.9852460311618</v>
+        <v>103.3662522847382</v>
       </c>
       <c r="D6" t="n">
-        <v>27.81389420901639</v>
+        <v>33.24786775202249</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="C7" t="n">
-        <v>155.525526063667</v>
+        <v>71.44472568115313</v>
       </c>
       <c r="D7" t="n">
-        <v>27.30829414132927</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>110.3189895262141</v>
+        <v>42.89255719854314</v>
       </c>
       <c r="D8" t="n">
-        <v>26.20284622634736</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>60.12811989430013</v>
+        <v>29.17656002251095</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.93362637120549</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.401174958138451</v>
+        <v>6.281221811771093</v>
       </c>
       <c r="C2" t="n">
-        <v>3.295727043156542</v>
+        <v>1.776963344686727</v>
       </c>
       <c r="D2" t="n">
-        <v>16.49434317905066</v>
+        <v>14.11164150084365</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.51285751671111</v>
+        <v>33.2125248346696</v>
       </c>
       <c r="C3" t="n">
-        <v>36.50628838241764</v>
+        <v>26.24211613451724</v>
       </c>
       <c r="D3" t="n">
-        <v>65.63965150594174</v>
+        <v>89.74646638372218</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.71612034921921</v>
+        <v>38.79866927183395</v>
       </c>
       <c r="C4" t="n">
-        <v>121.7180621202238</v>
+        <v>100.5829975431985</v>
       </c>
       <c r="D4" t="n">
-        <v>85.43364871896593</v>
+        <v>138.6031408855647</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.85142160595602</v>
+        <v>40.05530633326987</v>
       </c>
       <c r="C5" t="n">
-        <v>178.7762569433442</v>
+        <v>148.0966411856314</v>
       </c>
       <c r="D5" t="n">
-        <v>57.0395416167397</v>
+        <v>91.22890541713487</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.5044637557294</v>
+        <v>40.73467574460867</v>
       </c>
       <c r="C6" t="n">
-        <v>192.2821601106676</v>
+        <v>133.8367557814464</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>41.94222542083224</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.51063197939536</v>
+        <v>21.97838585497334</v>
       </c>
       <c r="C7" t="n">
-        <v>189.3015740805742</v>
+        <v>100.3100716814179</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>142.8639259219958</v>
+        <v>58.41398840268521</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>62.56874468705769</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32480392585223</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.878885179479147</v>
+        <v>6.862416452685205</v>
       </c>
       <c r="C2" t="n">
-        <v>8.334056261351174</v>
+        <v>6.074073046175016</v>
       </c>
       <c r="D2" t="n">
-        <v>15.32802690640545</v>
+        <v>21.23618459056275</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.23734626471625</v>
+        <v>27.21404636172158</v>
       </c>
       <c r="C3" t="n">
-        <v>24.46024405130928</v>
+        <v>15.78650308428871</v>
       </c>
       <c r="D3" t="n">
-        <v>64.14739499548659</v>
+        <v>81.66668277777092</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.24612524079224</v>
+        <v>51.06364334098934</v>
       </c>
       <c r="C4" t="n">
-        <v>106.5687132959913</v>
+        <v>83.30227445304611</v>
       </c>
       <c r="D4" t="n">
-        <v>95.0950278764588</v>
+        <v>149.8470973423034</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.20194659410114</v>
+        <v>48.47379289718628</v>
       </c>
       <c r="C5" t="n">
-        <v>200.0065510476815</v>
+        <v>166.3326047920159</v>
       </c>
       <c r="D5" t="n">
-        <v>71.76575718044185</v>
+        <v>114.4963260077843</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.69692736349078</v>
+        <v>47.05418571684538</v>
       </c>
       <c r="C6" t="n">
-        <v>235.9149550782128</v>
+        <v>181.6959746157742</v>
       </c>
       <c r="D6" t="n">
-        <v>40.8151790563569</v>
+        <v>57.88188114698346</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.99645822427728</v>
+        <v>32.87774886752143</v>
       </c>
       <c r="C7" t="n">
-        <v>230.8628813921587</v>
+        <v>144.805822880996</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C8" t="n">
-        <v>190.3461536378928</v>
+        <v>92.37755023110363</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>108.0531158248124</v>
+        <v>51.58593311964863</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>49.82369599052563</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.9050578767911</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.338523031515902</v>
+        <v>4.059526757060561</v>
       </c>
       <c r="C2" t="n">
-        <v>4.07228947721577</v>
+        <v>2.789145227765188</v>
       </c>
       <c r="D2" t="n">
-        <v>10.70301347169872</v>
+        <v>14.67909167389831</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.60902773399829</v>
+        <v>27.89636101617312</v>
       </c>
       <c r="C3" t="n">
-        <v>29.30026023324605</v>
+        <v>20.29763378530281</v>
       </c>
       <c r="D3" t="n">
-        <v>64.00504157837081</v>
+        <v>82.45208094116838</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.81968688425063</v>
+        <v>56.60266388834985</v>
       </c>
       <c r="C4" t="n">
-        <v>101.3742861928214</v>
+        <v>76.15515116612933</v>
       </c>
       <c r="D4" t="n">
-        <v>103.6715758207589</v>
+        <v>160.4912059517473</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.42913122440965</v>
+        <v>50.65818153913543</v>
       </c>
       <c r="C5" t="n">
-        <v>236.8711773421492</v>
+        <v>189.3545884566036</v>
       </c>
       <c r="D5" t="n">
-        <v>75.69274799742909</v>
+        <v>120.9022297779947</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.73339089726815</v>
+        <v>39.52712606838509</v>
       </c>
       <c r="C6" t="n">
-        <v>273.8320149116332</v>
+        <v>215.386610582412</v>
       </c>
       <c r="D6" t="n">
-        <v>40.45291415348983</v>
+        <v>56.47307319138928</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>244.3373686329462</v>
+        <v>140.6736467938212</v>
       </c>
       <c r="D7" t="n">
-        <v>32.27888276793088</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>133.6845848872882</v>
+        <v>66.92574099850506</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.01350778814797</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.96293993361265</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.368957210347553</v>
+        <v>5.439864029231576</v>
       </c>
       <c r="C2" t="n">
-        <v>11.09178556258046</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="D2" t="n">
-        <v>15.52633994266331</v>
+        <v>12.86384016874596</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.56775327269092</v>
+        <v>21.15175428799753</v>
       </c>
       <c r="C3" t="n">
-        <v>22.44275251908209</v>
+        <v>15.42816517223863</v>
       </c>
       <c r="D3" t="n">
-        <v>58.46307578789757</v>
+        <v>75.67802178186538</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.04566878267665</v>
+        <v>54.95627298832795</v>
       </c>
       <c r="C4" t="n">
-        <v>88.62432875776805</v>
+        <v>64.06885517914685</v>
       </c>
       <c r="D4" t="n">
-        <v>110.1550376596049</v>
+        <v>164.3965983192411</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.38757902566179</v>
+        <v>65.21259125459439</v>
       </c>
       <c r="C5" t="n">
-        <v>216.1072133973292</v>
+        <v>167.8543137335984</v>
       </c>
       <c r="D5" t="n">
-        <v>91.17981803192252</v>
+        <v>147.2130682518092</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.94472869558847</v>
+        <v>51.20010627187966</v>
       </c>
       <c r="C6" t="n">
-        <v>320.3226774462408</v>
+        <v>255.6785181124054</v>
       </c>
       <c r="D6" t="n">
-        <v>51.56237117474674</v>
+        <v>74.78757661411353</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>21.97838585497334</v>
       </c>
       <c r="C7" t="n">
-        <v>311.3504851771292</v>
+        <v>215.5917958525995</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>42.16017341117502</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>207.1193131649496</v>
+        <v>114.9921085984289</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>81.53905557621881</v>
+        <v>47.8140584399324</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.64050041379642</v>
+        <v>3.71198806975719</v>
       </c>
       <c r="C2" t="n">
-        <v>6.939974521320702</v>
+        <v>2.587886948394592</v>
       </c>
       <c r="D2" t="n">
-        <v>11.29206209424681</v>
+        <v>9.841038987370027</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.44717823151781</v>
+        <v>20.26327261565417</v>
       </c>
       <c r="C3" t="n">
-        <v>32.00006641992479</v>
+        <v>17.30330328735003</v>
       </c>
       <c r="D3" t="n">
-        <v>57.52059799182062</v>
+        <v>70.19496085364695</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.01264921363074</v>
+        <v>50.57865997509143</v>
       </c>
       <c r="C4" t="n">
-        <v>76.8571007746658</v>
+        <v>54.68825586506858</v>
       </c>
       <c r="D4" t="n">
-        <v>113.0777005751476</v>
+        <v>165.3155141704162</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.22268646907735</v>
+        <v>73.11566027378122</v>
       </c>
       <c r="C5" t="n">
-        <v>204.1053477129119</v>
+        <v>154.5025449558418</v>
       </c>
       <c r="D5" t="n">
-        <v>102.8871594050658</v>
+        <v>165.0072453912827</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>60.73974871404592</v>
       </c>
       <c r="C6" t="n">
-        <v>343.7491411649783</v>
+        <v>272.4634586119131</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>89.72094094341176</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.65414707066464</v>
+        <v>20.48122060599696</v>
       </c>
       <c r="C7" t="n">
-        <v>369.7998164971673</v>
+        <v>270.6275904049715</v>
       </c>
       <c r="D7" t="n">
-        <v>38.5669768136317</v>
+        <v>48.14883440708056</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>259.9422483919492</v>
+        <v>155.5481062608646</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>88.86092995449152</v>
+        <v>57.13280764864312</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.44775906859456</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.411172361630166</v>
+        <v>5.984734005088556</v>
       </c>
       <c r="C2" t="n">
-        <v>8.170104394741955</v>
+        <v>4.602433237509047</v>
       </c>
       <c r="D2" t="n">
-        <v>17.53695924096077</v>
+        <v>10.04622425755761</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.732645829275379</v>
+        <v>16.54244881655876</v>
       </c>
       <c r="C3" t="n">
-        <v>29.75186417719959</v>
+        <v>13.79355524466769</v>
       </c>
       <c r="D3" t="n">
-        <v>53.80959166976768</v>
+        <v>63.18037350680348</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.32047602440774</v>
+        <v>44.59294422229862</v>
       </c>
       <c r="C4" t="n">
-        <v>77.81430478630644</v>
+        <v>49.35343884019141</v>
       </c>
       <c r="D4" t="n">
-        <v>114.5326506728414</v>
+        <v>162.7629701393745</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.41903600992671</v>
+        <v>74.7846313710008</v>
       </c>
       <c r="C5" t="n">
-        <v>178.2362957060084</v>
+        <v>130.9160563613122</v>
       </c>
       <c r="D5" t="n">
-        <v>113.0482481440202</v>
+        <v>178.9480627915874</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.67683474551611</v>
+        <v>74.18380177600174</v>
       </c>
       <c r="C6" t="n">
-        <v>337.6711411279863</v>
+        <v>262.6018029227538</v>
       </c>
       <c r="D6" t="n">
-        <v>72.29197394991814</v>
+        <v>112.8656430710303</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.09248957284423</v>
+        <v>38.38731698375453</v>
       </c>
       <c r="C7" t="n">
-        <v>419.5655893731424</v>
+        <v>324.6453125880395</v>
       </c>
       <c r="D7" t="n">
-        <v>44.01665831990574</v>
+        <v>58.50921792999716</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.009678608322226</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>347.3963338862551</v>
+        <v>233.5725050558799</v>
       </c>
       <c r="D8" t="n">
-        <v>35.21529015133309</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>166.739048341574</v>
+        <v>107.498428371913</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>55.94489292650449</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.061490252469055</v>
+        <v>7.022441328477434</v>
       </c>
       <c r="C2" t="n">
-        <v>17.50063457590364</v>
+        <v>2.756747553525043</v>
       </c>
       <c r="D2" t="n">
-        <v>7.025386571590175</v>
+        <v>14.53182951826129</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.761255381418778</v>
+        <v>4.28140173822034</v>
       </c>
       <c r="C2" t="n">
-        <v>4.836089191119788</v>
+        <v>2.614394136409256</v>
       </c>
       <c r="D2" t="n">
-        <v>13.04840873714436</v>
+        <v>7.39354196068273</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.92332586807751</v>
+        <v>22.13350199224434</v>
       </c>
       <c r="C3" t="n">
-        <v>35.0582105186536</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D3" t="n">
-        <v>59.95042355983148</v>
+        <v>68.07438581247384</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.168788156335</v>
+        <v>58.78508903489051</v>
       </c>
       <c r="C4" t="n">
-        <v>111.0356653503143</v>
+        <v>72.0710807164626</v>
       </c>
       <c r="D4" t="n">
-        <v>115.2601257216883</v>
+        <v>166.7449388277995</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.01064466049325</v>
+        <v>43.85957868722626</v>
       </c>
       <c r="C5" t="n">
-        <v>276.6565030567512</v>
+        <v>210.9775816426396</v>
       </c>
       <c r="D5" t="n">
-        <v>103.4025769497953</v>
+        <v>164.2709346130976</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.57739082328414</v>
+        <v>23.82898027747859</v>
       </c>
       <c r="C6" t="n">
-        <v>335.900068269525</v>
+        <v>265.2986638663199</v>
       </c>
       <c r="D6" t="n">
-        <v>60.21647718768238</v>
+        <v>88.79515285830703</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.611268966847268</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>244.2774820229871</v>
+        <v>164.2689711176891</v>
       </c>
       <c r="D7" t="n">
-        <v>29.88341836956866</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>122.8362727553609</v>
+        <v>79.19267856306895</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>24.95111790343269</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>18.50594422505238</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74879576089983</v>
+        <v>16.17036643664921</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.361144286442584</v>
+        <v>7.004769869800992</v>
       </c>
       <c r="C2" t="n">
-        <v>8.464628706015999</v>
+        <v>2.682134728002286</v>
       </c>
       <c r="D2" t="n">
-        <v>10.41241615124167</v>
+        <v>21.38737373701677</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.634471058850698</v>
+        <v>14.91274762750905</v>
       </c>
       <c r="C3" t="n">
-        <v>44.10010687476672</v>
+        <v>6.945865007546184</v>
       </c>
       <c r="D3" t="n">
-        <v>9.036987617591889</v>
+        <v>15.34471661737765</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39709530583433</v>
+        <v>13.397828412131</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13773424819152</v>
+        <v>70.14157227527406</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576128859509922</v>
+        <v>1.576215107309529</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.661338099763856</v>
+        <v>4.87535909928966</v>
       </c>
       <c r="C2" t="n">
-        <v>9.069385291832035</v>
+        <v>6.474626109507715</v>
       </c>
       <c r="D2" t="n">
-        <v>13.64531134132642</v>
+        <v>21.99409381824129</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61884521104076</v>
+        <v>20.5136182802371</v>
       </c>
       <c r="C3" t="n">
-        <v>37.16405934426301</v>
+        <v>9.140071126537805</v>
       </c>
       <c r="D3" t="n">
-        <v>15.59997102048182</v>
+        <v>29.59969328304133</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.18465068385641</v>
+        <v>17.26796036999714</v>
       </c>
       <c r="C4" t="n">
-        <v>67.7317558636917</v>
+        <v>11.14185469549705</v>
       </c>
       <c r="D4" t="n">
-        <v>19.80774168088364</v>
+        <v>23.11328620108265</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.092505268377454</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43649389349136</v>
+        <v>15.44105656736608</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11938698474128</v>
+        <v>86.14484190214763</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249788188103444</v>
+        <v>3.250748751024439</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.407065444363932</v>
+        <v>6.791730617979434</v>
       </c>
       <c r="C2" t="n">
-        <v>8.447938995043803</v>
+        <v>7.246279805045707</v>
       </c>
       <c r="D2" t="n">
-        <v>11.22530325035803</v>
+        <v>23.237968159522</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.19531103988288</v>
+        <v>18.4666743168825</v>
       </c>
       <c r="C3" t="n">
-        <v>36.0252320073367</v>
+        <v>18.87409961414493</v>
       </c>
       <c r="D3" t="n">
-        <v>22.89435646303562</v>
+        <v>40.32528695193773</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.38955821660351</v>
+        <v>29.9158160438088</v>
       </c>
       <c r="C4" t="n">
-        <v>82.40888404218151</v>
+        <v>18.05924901962008</v>
       </c>
       <c r="D4" t="n">
-        <v>23.18986252201391</v>
+        <v>32.73637719810989</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.40023426816321</v>
+        <v>15.11891464540088</v>
       </c>
       <c r="C5" t="n">
-        <v>72.40389318820228</v>
+        <v>14.01444847812322</v>
       </c>
       <c r="D5" t="n">
-        <v>30.09056713516474</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5235,7 +5235,7 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
         <v>41.15780900513902</v>
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72182609863513</v>
+        <v>16.73676718784788</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1670478967425</v>
+        <v>102.0942798458721</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180456524658783</v>
+        <v>5.021030156354364</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.022621254926682</v>
+        <v>6.34994415106837</v>
       </c>
       <c r="C2" t="n">
-        <v>4.962734644967626</v>
+        <v>10.09825688588269</v>
       </c>
       <c r="D2" t="n">
-        <v>17.61451730959627</v>
+        <v>20.43606021160161</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.01721379478671</v>
+        <v>21.10266690278519</v>
       </c>
       <c r="C3" t="n">
-        <v>34.14518515370406</v>
+        <v>24.48969648243668</v>
       </c>
       <c r="D3" t="n">
-        <v>26.33047342789946</v>
+        <v>49.01375413452201</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.15005283449629</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="C4" t="n">
-        <v>86.63334441355555</v>
+        <v>34.17856457564846</v>
       </c>
       <c r="D4" t="n">
-        <v>29.11176467403067</v>
+        <v>44.56741878198821</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.5311098124643</v>
+        <v>30.36054775383262</v>
       </c>
       <c r="C5" t="n">
-        <v>113.9809084630547</v>
+        <v>24.64186737659495</v>
       </c>
       <c r="D5" t="n">
-        <v>31.66136346195964</v>
+        <v>35.66198535676539</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.338384162795663</v>
+        <v>13.16229147083699</v>
       </c>
       <c r="C6" t="n">
-        <v>65.32843748369551</v>
+        <v>17.54972196111598</v>
       </c>
       <c r="D6" t="n">
-        <v>37.39378830705677</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03425764232279</v>
+        <v>18.06683347324659</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7932875883762</v>
+        <v>117.8645802778468</v>
       </c>
       <c r="D21" t="n">
-        <v>6.011419214107597</v>
+        <v>6.882603227903464</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.215444715586557</v>
+        <v>6.529603980945535</v>
       </c>
       <c r="C2" t="n">
-        <v>16.88998750386213</v>
+        <v>10.38100022470577</v>
       </c>
       <c r="D2" t="n">
-        <v>19.24520024635022</v>
+        <v>29.74695543867836</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.76548547187203</v>
+        <v>19.20789383358884</v>
       </c>
       <c r="C3" t="n">
-        <v>24.25407703341745</v>
+        <v>31.13612844018759</v>
       </c>
       <c r="D3" t="n">
-        <v>31.39138284329177</v>
+        <v>50.47164947532852</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.86253962587222</v>
+        <v>27.43984833369835</v>
       </c>
       <c r="C4" t="n">
-        <v>71.06282582420111</v>
+        <v>41.59370498582462</v>
       </c>
       <c r="D4" t="n">
-        <v>30.24764676784423</v>
+        <v>50.51484637431538</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.95402208881642</v>
+        <v>24.54369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>102.5680914011855</v>
+        <v>33.94392687433348</v>
       </c>
       <c r="D5" t="n">
-        <v>28.24979018970198</v>
+        <v>35.41654843070369</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.6666888066416</v>
+        <v>15.01386764104647</v>
       </c>
       <c r="C6" t="n">
-        <v>83.20017269180445</v>
+        <v>19.48180144307371</v>
       </c>
       <c r="D6" t="n">
-        <v>29.94723197034471</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>36.77037851486003</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.041901468375008</v>
+        <v>7.063556815741327</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0178262660157</v>
+        <v>66.22084514757493</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40118841773438</v>
+        <v>5.297667611805995</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.98040610364407</v>
+        <v>5.993569734426777</v>
       </c>
       <c r="C2" t="n">
-        <v>8.278096642209105</v>
+        <v>8.08272884906399</v>
       </c>
       <c r="D2" t="n">
-        <v>22.82072538521711</v>
+        <v>34.69300037267379</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.83973844449629</v>
+        <v>21.52972715413255</v>
       </c>
       <c r="C3" t="n">
-        <v>50.73181261695393</v>
+        <v>37.3358651925062</v>
       </c>
       <c r="D3" t="n">
-        <v>39.97185777840889</v>
+        <v>63.96577167020094</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.98489823600458</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="C4" t="n">
-        <v>64.80909294814894</v>
+        <v>64.91119470939061</v>
       </c>
       <c r="D4" t="n">
-        <v>39.67929696254333</v>
+        <v>66.02155136289375</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.4889357189107</v>
+        <v>34.26299487821369</v>
       </c>
       <c r="C5" t="n">
-        <v>120.0677442293849</v>
+        <v>60.62292073724056</v>
       </c>
       <c r="D5" t="n">
-        <v>32.86400439966199</v>
+        <v>46.78027810736052</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.80381469006666</v>
+        <v>25.80131141531043</v>
       </c>
       <c r="C6" t="n">
-        <v>129.5298286029157</v>
+        <v>40.05039759474864</v>
       </c>
       <c r="D6" t="n">
-        <v>32.6440929139107</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.222537933694536</v>
+        <v>12.87562114119692</v>
       </c>
       <c r="C7" t="n">
-        <v>84.5000066522272</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>35.71598148049896</v>
+        <v>19.86075605691297</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>22.85312305945724</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.256890386090404</v>
+        <v>7.287859095863181</v>
       </c>
       <c r="C21" t="n">
-        <v>75.29023775568795</v>
+        <v>75.6115381195805</v>
       </c>
       <c r="D21" t="n">
-        <v>5.442667789567803</v>
+        <v>6.376876708880283</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.11548637620263</v>
+        <v>5.560618996853934</v>
       </c>
       <c r="C2" t="n">
-        <v>6.864379948093698</v>
+        <v>5.080544369477244</v>
       </c>
       <c r="D2" t="n">
-        <v>20.42526098685489</v>
+        <v>34.12653194732337</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86780821729195</v>
+        <v>21.09775816426395</v>
       </c>
       <c r="C3" t="n">
-        <v>40.30074325933157</v>
+        <v>33.76721228756904</v>
       </c>
       <c r="D3" t="n">
-        <v>48.42470551197393</v>
+        <v>76.8757539810465</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.56220694383071</v>
+        <v>38.4285503873329</v>
       </c>
       <c r="C4" t="n">
-        <v>98.89831848271095</v>
+        <v>81.77074803442109</v>
       </c>
       <c r="D4" t="n">
-        <v>49.8001340456237</v>
+        <v>83.26398629258047</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.79666471869646</v>
+        <v>43.83503499462009</v>
       </c>
       <c r="C5" t="n">
-        <v>119.9695694589603</v>
+        <v>93.90416791120742</v>
       </c>
       <c r="D5" t="n">
-        <v>39.785325714602</v>
+        <v>59.51845456996289</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.73968229412113</v>
+        <v>36.99127174831558</v>
       </c>
       <c r="C6" t="n">
-        <v>162.375179796197</v>
+        <v>71.48694083243576</v>
       </c>
       <c r="D6" t="n">
-        <v>35.86422538384024</v>
+        <v>42.9082651618111</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>22.69702517448201</v>
       </c>
       <c r="C7" t="n">
-        <v>137.6793162958684</v>
+        <v>42.27994663109313</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>75.8547363686298</v>
+        <v>25.95250056176443</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>24.62812290873548</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.456439697630374</v>
+        <v>7.498320129728268</v>
       </c>
       <c r="C21" t="n">
-        <v>83.88494659834171</v>
+        <v>85.29339147565905</v>
       </c>
       <c r="D21" t="n">
-        <v>6.524384735426578</v>
+        <v>7.498320129728268</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_19_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497620096166</v>
+        <v>10.84497645391778</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907148456001</v>
+        <v>37.78907236597986</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.099598486485433</v>
+        <v>0.5576326960121883</v>
       </c>
       <c r="C2" t="n">
-        <v>5.079562621772997</v>
+        <v>3.150428382928014</v>
       </c>
       <c r="D2" t="n">
-        <v>24.97958858685584</v>
+        <v>17.9591107537869</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.89511722656161</v>
+        <v>5.267076433284138</v>
       </c>
       <c r="C3" t="n">
-        <v>25.88377822246716</v>
+        <v>37.85619147575701</v>
       </c>
       <c r="D3" t="n">
-        <v>85.08316478854982</v>
+        <v>83.77253160338034</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.36022895866312</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C4" t="n">
-        <v>82.3961213220263</v>
+        <v>105.815712806834</v>
       </c>
       <c r="D4" t="n">
-        <v>100.0724887369901</v>
+        <v>94.20163746559419</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.17359908386501</v>
+        <v>12.37002107350981</v>
       </c>
       <c r="C5" t="n">
-        <v>124.1665408946154</v>
+        <v>137.7392029058275</v>
       </c>
       <c r="D5" t="n">
-        <v>75.07915568227483</v>
+        <v>52.0817157102933</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.06047711369836</v>
+        <v>9.217629195173304</v>
       </c>
       <c r="C6" t="n">
-        <v>111.0945702125691</v>
+        <v>105.2983317666959</v>
       </c>
       <c r="D6" t="n">
-        <v>50.79758971313847</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.41672835715293</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>72.58257127037518</v>
+        <v>54.73636150257666</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8426679920758</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.60764507566654</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>41.39048321104552</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>37.43894870145212</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.693734879940873</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.24825227927569</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.655451739933483</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.157742585214248</v>
+        <v>1.2311116211255</v>
       </c>
       <c r="C2" t="n">
-        <v>6.211517724769569</v>
+        <v>6.493279315888404</v>
       </c>
       <c r="D2" t="n">
-        <v>25.93973784160922</v>
+        <v>20.84348550886403</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.07674055184727</v>
+        <v>3.490113088597411</v>
       </c>
       <c r="C3" t="n">
-        <v>22.58019719767664</v>
+        <v>23.40977400776519</v>
       </c>
       <c r="D3" t="n">
-        <v>84.77882300023332</v>
+        <v>78.79016200432777</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.61999118966102</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="C4" t="n">
-        <v>73.4239290529147</v>
+        <v>99.70236985248908</v>
       </c>
       <c r="D4" t="n">
-        <v>116.7916521403133</v>
+        <v>113.8817519449258</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.63425974133501</v>
+        <v>14.45623494503429</v>
       </c>
       <c r="C5" t="n">
-        <v>136.1684065790326</v>
+        <v>169.6460032938488</v>
       </c>
       <c r="D5" t="n">
-        <v>90.09989555725103</v>
+        <v>72.796592269901</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.7611261793611</v>
+        <v>12.84027822384404</v>
       </c>
       <c r="C6" t="n">
-        <v>151.7487426454295</v>
+        <v>163.0997096019311</v>
       </c>
       <c r="D6" t="n">
-        <v>61.22276858453534</v>
+        <v>39.04410619789565</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.85507085933252</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>112.7065999429423</v>
+        <v>102.1665565901486</v>
       </c>
       <c r="D7" t="n">
-        <v>45.09461729916874</v>
+        <v>31.68001666834032</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.03594911662541</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>67.09263810822702</v>
+        <v>50.40292713603124</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>37.86600895279948</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.874105827757782</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3633757608512</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.842632284697226</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12.17858027118168</v>
+        <v>0.6597344572538566</v>
       </c>
       <c r="C2" t="n">
-        <v>6.092726252555705</v>
+        <v>2.783254741539707</v>
       </c>
       <c r="D2" t="n">
-        <v>24.72237068834318</v>
+        <v>14.18429083095792</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.52405765208533</v>
+        <v>4.088979188187966</v>
       </c>
       <c r="C3" t="n">
-        <v>23.12997591205485</v>
+        <v>25.91323065359456</v>
       </c>
       <c r="D3" t="n">
-        <v>85.78020565856507</v>
+        <v>79.82099709378691</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.62449901755476</v>
+        <v>11.55026174046372</v>
       </c>
       <c r="C4" t="n">
-        <v>65.39617807528853</v>
+        <v>93.6145523384546</v>
       </c>
       <c r="D4" t="n">
-        <v>127.0401164249458</v>
+        <v>125.4830645660103</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.7141822160065</v>
+        <v>14.89802141194535</v>
       </c>
       <c r="C5" t="n">
-        <v>134.1312800927205</v>
+        <v>197.9939682539755</v>
       </c>
       <c r="D5" t="n">
-        <v>105.8569462104124</v>
+        <v>82.71224408279379</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.00642423670256</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="C6" t="n">
-        <v>179.924901757313</v>
+        <v>200.171484661995</v>
       </c>
       <c r="D6" t="n">
-        <v>72.8554971321558</v>
+        <v>39.40637110076273</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>54.73636150257666</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>156.9628047026843</v>
+        <v>94.44118390543041</v>
       </c>
       <c r="D7" t="n">
-        <v>50.48441219548373</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.38218726105504</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>101.6403398206723</v>
+        <v>42.55876297909923</v>
       </c>
       <c r="D8" t="n">
-        <v>41.80772598535042</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.19374845510188</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>58.242182554442</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>38.29306920414684</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.41280136633594</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.038779218519894</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.5332142546485</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.05332142546485</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.79824299901067</v>
+        <v>0.4673119072214817</v>
       </c>
       <c r="C2" t="n">
-        <v>4.142975311921539</v>
+        <v>5.804092427507142</v>
       </c>
       <c r="D2" t="n">
-        <v>20.43606021160161</v>
+        <v>17.09320927864121</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.99944452511903</v>
+        <v>3.180862561759666</v>
       </c>
       <c r="C3" t="n">
-        <v>36.00068831473054</v>
+        <v>17.70091110756999</v>
       </c>
       <c r="D3" t="n">
-        <v>94.06124754388691</v>
+        <v>73.04693793448392</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.7634241654723</v>
+        <v>9.801769079200154</v>
       </c>
       <c r="C4" t="n">
-        <v>103.3652705370339</v>
+        <v>79.20544128322416</v>
       </c>
       <c r="D4" t="n">
-        <v>120.9778243512217</v>
+        <v>135.8463933320397</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.61918936840603</v>
+        <v>16.44427404613408</v>
       </c>
       <c r="C5" t="n">
-        <v>107.5013736150258</v>
+        <v>187.1456561220483</v>
       </c>
       <c r="D5" t="n">
-        <v>71.98665041389738</v>
+        <v>106.8632376072653</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.97239755775664</v>
+        <v>14.61135108230528</v>
       </c>
       <c r="C6" t="n">
-        <v>103.3662522847382</v>
+        <v>258.2948757442231</v>
       </c>
       <c r="D6" t="n">
-        <v>33.24786775202249</v>
+        <v>52.72966919509619</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.41566449399068</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>71.44472568115313</v>
+        <v>180.9773352962655</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>42.89255719854314</v>
+        <v>78.69198723390308</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>29.17656002251095</v>
+        <v>37.05312185368311</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.281221811771093</v>
+        <v>0.2689988709636261</v>
       </c>
       <c r="C2" t="n">
-        <v>1.776963344686727</v>
+        <v>3.904410619789565</v>
       </c>
       <c r="D2" t="n">
-        <v>14.11164150084365</v>
+        <v>12.50844749980861</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>33.2125248346696</v>
+        <v>2.523091599914303</v>
       </c>
       <c r="C3" t="n">
-        <v>26.24211613451724</v>
+        <v>20.54797944988574</v>
       </c>
       <c r="D3" t="n">
-        <v>89.74646638372218</v>
+        <v>70.54348128865456</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.79866927183395</v>
+        <v>8.576547944300136</v>
       </c>
       <c r="C4" t="n">
-        <v>100.5829975431985</v>
+        <v>65.17921183264998</v>
       </c>
       <c r="D4" t="n">
-        <v>138.6031408855647</v>
+        <v>140.7983287522605</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.05530633326987</v>
+        <v>16.76334205001429</v>
       </c>
       <c r="C5" t="n">
-        <v>148.0966411856314</v>
+        <v>176.7145867644259</v>
       </c>
       <c r="D5" t="n">
-        <v>91.22890541713487</v>
+        <v>124.9273953654066</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.73467574460867</v>
+        <v>17.30821202587127</v>
       </c>
       <c r="C6" t="n">
-        <v>133.8367557814464</v>
+        <v>285.3439884916313</v>
       </c>
       <c r="D6" t="n">
-        <v>41.94222542083224</v>
+        <v>64.84541761320608</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>100.3100716814179</v>
+        <v>249.0684108197115</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>40.96244121199391</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>58.41398840268521</v>
+        <v>119.1645363414778</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>47.14843349645305</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.862416452685205</v>
+        <v>0.6685701865920778</v>
       </c>
       <c r="C2" t="n">
-        <v>6.074073046175016</v>
+        <v>4.674100819919064</v>
       </c>
       <c r="D2" t="n">
-        <v>21.23618459056275</v>
+        <v>11.87325673516092</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.21404636172158</v>
+        <v>1.737693436516855</v>
       </c>
       <c r="C3" t="n">
-        <v>15.78650308428871</v>
+        <v>17.74999849278233</v>
       </c>
       <c r="D3" t="n">
-        <v>81.66668277777092</v>
+        <v>64.88861451219293</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.06364334098934</v>
+        <v>6.853580723346983</v>
       </c>
       <c r="C4" t="n">
-        <v>83.30227445304611</v>
+        <v>58.40220743023426</v>
       </c>
       <c r="D4" t="n">
-        <v>149.8470973423034</v>
+        <v>143.0573302197325</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.47379289718628</v>
+        <v>15.2661768010379</v>
       </c>
       <c r="C5" t="n">
-        <v>166.3326047920159</v>
+        <v>150.3301172127929</v>
       </c>
       <c r="D5" t="n">
-        <v>114.4963260077843</v>
+        <v>142.1079801897258</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.05418571684538</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>181.6959746157742</v>
+        <v>287.3968229412113</v>
       </c>
       <c r="D6" t="n">
-        <v>57.88188114698346</v>
+        <v>82.15362963907737</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.87774886752143</v>
+        <v>12.33664165156542</v>
       </c>
       <c r="C7" t="n">
-        <v>144.805822880996</v>
+        <v>319.4351775216017</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>48.50815406683489</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>92.37755023110363</v>
+        <v>207.3696588295325</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>51.58593311964863</v>
+        <v>86.75311763347362</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>35.44600086183109</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
         <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.059526757060561</v>
+        <v>0.4594579255875073</v>
       </c>
       <c r="C2" t="n">
-        <v>2.789145227765188</v>
+        <v>2.541744806294992</v>
       </c>
       <c r="D2" t="n">
-        <v>14.67909167389831</v>
+        <v>8.643306788188918</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.89636101617312</v>
+        <v>2.64090132442392</v>
       </c>
       <c r="C3" t="n">
-        <v>20.29763378530281</v>
+        <v>20.63633674326795</v>
       </c>
       <c r="D3" t="n">
-        <v>82.45208094116838</v>
+        <v>69.73353943265094</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>56.60266388834985</v>
+        <v>10.68239676990954</v>
       </c>
       <c r="C4" t="n">
-        <v>76.15515116612933</v>
+        <v>84.02974950189299</v>
       </c>
       <c r="D4" t="n">
-        <v>160.4912059517473</v>
+        <v>145.4056707282908</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.65818153913543</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C5" t="n">
-        <v>189.3545884566036</v>
+        <v>234.6867887002001</v>
       </c>
       <c r="D5" t="n">
-        <v>120.9022297779947</v>
+        <v>129.0998231084556</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.52712606838509</v>
+        <v>7.647814616082655</v>
       </c>
       <c r="C6" t="n">
-        <v>215.386610582412</v>
+        <v>275.1603195554791</v>
       </c>
       <c r="D6" t="n">
-        <v>56.47307319138928</v>
+        <v>68.50831829775093</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>3.653083207502381</v>
       </c>
       <c r="C7" t="n">
-        <v>140.6736467938212</v>
+        <v>145.8238952503</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>35.15344004596554</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>66.92574099850506</v>
+        <v>63.92159302350981</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>27.06874770149305</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>23.77302065833652</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.439864029231576</v>
+        <v>0.2238384765682727</v>
       </c>
       <c r="C2" t="n">
-        <v>4.923464736797754</v>
+        <v>2.106830573313655</v>
       </c>
       <c r="D2" t="n">
-        <v>12.86384016874596</v>
+        <v>7.63014315740621</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.15175428799753</v>
+        <v>2.12057504117311</v>
       </c>
       <c r="C3" t="n">
-        <v>15.42816517223863</v>
+        <v>14.93238258159398</v>
       </c>
       <c r="D3" t="n">
-        <v>75.67802178186538</v>
+        <v>61.22669557535232</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.95627298832795</v>
+        <v>7.440665850486576</v>
       </c>
       <c r="C4" t="n">
-        <v>64.06885517914685</v>
+        <v>65.43446623575416</v>
       </c>
       <c r="D4" t="n">
-        <v>164.3965983192411</v>
+        <v>140.7089897111741</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.21259125459439</v>
+        <v>10.99557428756428</v>
       </c>
       <c r="C5" t="n">
-        <v>167.8543137335984</v>
+        <v>176.9354799978814</v>
       </c>
       <c r="D5" t="n">
-        <v>147.2130682518092</v>
+        <v>133.2967945441107</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.20010627187966</v>
+        <v>7.124543089719105</v>
       </c>
       <c r="C6" t="n">
-        <v>255.6785181124054</v>
+        <v>265.5804254574387</v>
       </c>
       <c r="D6" t="n">
-        <v>74.78757661411353</v>
+        <v>74.3045567436241</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>2.87455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>215.5917958525995</v>
+        <v>182.6541603751191</v>
       </c>
       <c r="D7" t="n">
-        <v>42.16017341117502</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.67588438887831</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>114.9921085984289</v>
+        <v>73.8519710519663</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>26.45319189093031</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>47.8140584399324</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>16.94005663677871</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.71198806975719</v>
+        <v>0.1384264262988003</v>
       </c>
       <c r="C2" t="n">
-        <v>2.587886948394592</v>
+        <v>5.288674882777567</v>
       </c>
       <c r="D2" t="n">
-        <v>9.841038987370027</v>
+        <v>14.9579080219044</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.26327261565417</v>
+        <v>1.394081740030471</v>
       </c>
       <c r="C3" t="n">
-        <v>17.30330328735003</v>
+        <v>10.96612185643687</v>
       </c>
       <c r="D3" t="n">
-        <v>70.19496085364695</v>
+        <v>53.40707511102649</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.57865997509143</v>
+        <v>5.704935909378214</v>
       </c>
       <c r="C4" t="n">
-        <v>54.68825586506858</v>
+        <v>50.13196476965913</v>
       </c>
       <c r="D4" t="n">
-        <v>165.3155141704162</v>
+        <v>139.7900738599991</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.11566027378122</v>
+        <v>11.33918598405066</v>
       </c>
       <c r="C5" t="n">
-        <v>154.5025449558418</v>
+        <v>146.746738092292</v>
       </c>
       <c r="D5" t="n">
-        <v>165.0072453912827</v>
+        <v>152.9562923216531</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.73974871404592</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>272.4634586119131</v>
+        <v>277.5754189079262</v>
       </c>
       <c r="D6" t="n">
-        <v>89.72094094341176</v>
+        <v>96.80523237725676</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.48122060599696</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>270.6275904049715</v>
+        <v>284.5811705254314</v>
       </c>
       <c r="D7" t="n">
-        <v>48.14883440708056</v>
+        <v>46.11268966847268</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>155.5481062608646</v>
+        <v>157.7177686872501</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>57.13280764864312</v>
+        <v>59.57343244140068</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>22.40937309713768</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.984734005088556</v>
+        <v>0.1237002107350981</v>
       </c>
       <c r="C2" t="n">
-        <v>4.602433237509047</v>
+        <v>9.255917355638928</v>
       </c>
       <c r="D2" t="n">
-        <v>10.04622425755761</v>
+        <v>16.86249856814322</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.54244881655876</v>
+        <v>0.9130253649495336</v>
       </c>
       <c r="C3" t="n">
-        <v>13.79355524466769</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D3" t="n">
-        <v>63.18037350680348</v>
+        <v>52.80820901143593</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.59294422229862</v>
+        <v>4.186172210908399</v>
       </c>
       <c r="C4" t="n">
-        <v>49.35343884019141</v>
+        <v>38.2881604656256</v>
       </c>
       <c r="D4" t="n">
-        <v>162.7629701393745</v>
+        <v>135.3741726862969</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.7846313710008</v>
+        <v>10.21017612416683</v>
       </c>
       <c r="C5" t="n">
-        <v>130.9160563613122</v>
+        <v>119.5277829920492</v>
       </c>
       <c r="D5" t="n">
-        <v>178.9480627915874</v>
+        <v>167.216177725838</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>74.18380177600174</v>
+        <v>12.92078153559227</v>
       </c>
       <c r="C6" t="n">
-        <v>262.6018029227538</v>
+        <v>257.7716042178595</v>
       </c>
       <c r="D6" t="n">
-        <v>112.8656430710303</v>
+        <v>118.2191133022882</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.38731698375453</v>
+        <v>8.863218273940204</v>
       </c>
       <c r="C7" t="n">
-        <v>324.6453125880395</v>
+        <v>342.3118625259609</v>
       </c>
       <c r="D7" t="n">
-        <v>58.50921792999716</v>
+        <v>60.96456893831842</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>3.588287859022091</v>
       </c>
       <c r="C8" t="n">
-        <v>233.5725050558799</v>
+        <v>259.0243142884784</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>107.498428371913</v>
+        <v>122.6968645813578</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>24.18437294641592</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>45.98015372839937</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.022441328477434</v>
+        <v>3.738495257771854</v>
       </c>
       <c r="C2" t="n">
-        <v>2.756747553525043</v>
+        <v>17.06375684751381</v>
       </c>
       <c r="D2" t="n">
-        <v>14.53182951826129</v>
+        <v>9.2029029796096</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.28140173822034</v>
+        <v>0.3131775176547325</v>
       </c>
       <c r="C2" t="n">
-        <v>2.614394136409256</v>
+        <v>21.31865139771949</v>
       </c>
       <c r="D2" t="n">
-        <v>7.39354196068273</v>
+        <v>20.43998720241859</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.13350199224434</v>
+        <v>0.662679700366597</v>
       </c>
       <c r="C3" t="n">
-        <v>17.12167996206437</v>
+        <v>25.56471021858694</v>
       </c>
       <c r="D3" t="n">
-        <v>68.07438581247384</v>
+        <v>53.37271394137785</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.78508903489051</v>
+        <v>2.999239236474006</v>
       </c>
       <c r="C4" t="n">
-        <v>72.0710807164626</v>
+        <v>39.0411609547829</v>
       </c>
       <c r="D4" t="n">
-        <v>166.7449388277995</v>
+        <v>131.5453566397344</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.85957868722626</v>
+        <v>8.639379797371932</v>
       </c>
       <c r="C5" t="n">
-        <v>210.9775816426396</v>
+        <v>96.06401286055042</v>
       </c>
       <c r="D5" t="n">
-        <v>164.2709346130976</v>
+        <v>173.9166058073225</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.82898027747859</v>
+        <v>13.32329809433347</v>
       </c>
       <c r="C6" t="n">
-        <v>265.2986638663199</v>
+        <v>229.3136835148573</v>
       </c>
       <c r="D6" t="n">
-        <v>88.79515285830703</v>
+        <v>139.1097227009561</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.886960145291375</v>
+        <v>11.67788894201581</v>
       </c>
       <c r="C7" t="n">
-        <v>164.2689711176891</v>
+        <v>355.7264631567893</v>
       </c>
       <c r="D7" t="n">
-        <v>34.19525428662065</v>
+        <v>75.45712854840984</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>79.19267856306895</v>
+        <v>346.4783997827843</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>207.3421698938135</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>85.83911052081987</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.17036643664921</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.60978849752428</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.004769869800992</v>
+        <v>3.336960446734909</v>
       </c>
       <c r="C2" t="n">
-        <v>2.682134728002286</v>
+        <v>10.35449303669111</v>
       </c>
       <c r="D2" t="n">
-        <v>21.38737373701677</v>
+        <v>28.90363416073034</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.91274762750905</v>
+        <v>6.03283964259665</v>
       </c>
       <c r="C3" t="n">
-        <v>6.945865007546184</v>
+        <v>33.6886724712293</v>
       </c>
       <c r="D3" t="n">
-        <v>15.34471661737765</v>
+        <v>9.316785713302229</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.397828412131</v>
+        <v>11.67732068383213</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14157227527406</v>
+        <v>59.94357951033828</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576215107309529</v>
+        <v>0.7784880455888089</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.87535909928966</v>
+        <v>1.991966091916778</v>
       </c>
       <c r="C2" t="n">
-        <v>6.474626109507715</v>
+        <v>6.439283192154829</v>
       </c>
       <c r="D2" t="n">
-        <v>21.99409381824129</v>
+        <v>23.80934532339365</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.5136182802371</v>
+        <v>9.621127501618743</v>
       </c>
       <c r="C3" t="n">
-        <v>9.140071126537805</v>
+        <v>38.14580704850982</v>
       </c>
       <c r="D3" t="n">
-        <v>29.59969328304133</v>
+        <v>32.40749171718721</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.26796036999714</v>
+        <v>7.453428570641784</v>
       </c>
       <c r="C4" t="n">
-        <v>11.14185469549705</v>
+        <v>54.4330014619644</v>
       </c>
       <c r="D4" t="n">
-        <v>23.11328620108265</v>
+        <v>19.10579207234717</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44105656736608</v>
+        <v>13.62400417095988</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14484190214763</v>
+        <v>73.72990492519465</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250748751024439</v>
+        <v>1.602824020112927</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.791730617979434</v>
+        <v>1.278235510929347</v>
       </c>
       <c r="C2" t="n">
-        <v>7.246279805045707</v>
+        <v>5.519385593275567</v>
       </c>
       <c r="D2" t="n">
-        <v>23.237968159522</v>
+        <v>32.55377212511998</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4666743168825</v>
+        <v>8.079783605951249</v>
       </c>
       <c r="C3" t="n">
-        <v>18.87409961414493</v>
+        <v>29.99239236474006</v>
       </c>
       <c r="D3" t="n">
-        <v>40.32528695193773</v>
+        <v>44.57625451132643</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.9158160438088</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C4" t="n">
-        <v>18.05924901962008</v>
+        <v>79.49898384679396</v>
       </c>
       <c r="D4" t="n">
-        <v>32.73637719810989</v>
+        <v>31.65154598491717</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.11891464540088</v>
+        <v>7.142214548395547</v>
       </c>
       <c r="C5" t="n">
-        <v>14.01444847812322</v>
+        <v>61.38377520803183</v>
       </c>
       <c r="D5" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04714925199963</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.27655941962388</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73676718784788</v>
+        <v>14.82698346036303</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0942798458721</v>
+        <v>87.31445815547119</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021030156354364</v>
+        <v>2.471163910060505</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.34994415106837</v>
+        <v>1.035743827980385</v>
       </c>
       <c r="C2" t="n">
-        <v>10.09825688588269</v>
+        <v>3.732604771546373</v>
       </c>
       <c r="D2" t="n">
-        <v>20.43606021160161</v>
+        <v>27.81291246131214</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.10266690278519</v>
+        <v>6.03283964259665</v>
       </c>
       <c r="C3" t="n">
-        <v>24.48969648243668</v>
+        <v>24.89712177969911</v>
       </c>
       <c r="D3" t="n">
-        <v>49.01375413452201</v>
+        <v>60.27440030223293</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.97886888105885</v>
+        <v>14.9579080219044</v>
       </c>
       <c r="C4" t="n">
-        <v>34.17856457564846</v>
+        <v>76.99749069637309</v>
       </c>
       <c r="D4" t="n">
-        <v>44.56741878198821</v>
+        <v>46.85194568977053</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.36054775383262</v>
+        <v>14.48077863764046</v>
       </c>
       <c r="C5" t="n">
-        <v>24.64186737659495</v>
+        <v>109.2930631752762</v>
       </c>
       <c r="D5" t="n">
-        <v>35.66198535676539</v>
+        <v>32.37313054753858</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.16229147083699</v>
+        <v>7.205046401467343</v>
       </c>
       <c r="C6" t="n">
-        <v>17.54972196111598</v>
+        <v>57.15735134124931</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>33.00635781677777</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.72643654788041</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.40156017323271</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06683347324659</v>
+        <v>16.05649871345636</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8645802778468</v>
+        <v>100.5643866790162</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882603227903464</v>
+        <v>3.380315518622392</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.529603980945535</v>
+        <v>1.156498795602743</v>
       </c>
       <c r="C2" t="n">
-        <v>10.38100022470577</v>
+        <v>7.678248794914303</v>
       </c>
       <c r="D2" t="n">
-        <v>29.74695543867836</v>
+        <v>29.40727073300896</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.20789383358884</v>
+        <v>4.687845287778519</v>
       </c>
       <c r="C3" t="n">
-        <v>31.13612844018759</v>
+        <v>19.20298509506761</v>
       </c>
       <c r="D3" t="n">
-        <v>50.47164947532852</v>
+        <v>68.58489461868218</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.43984833369835</v>
+        <v>13.14560175986479</v>
       </c>
       <c r="C4" t="n">
-        <v>41.59370498582462</v>
+        <v>68.29331555052087</v>
       </c>
       <c r="D4" t="n">
-        <v>50.51484637431538</v>
+        <v>63.95399069774997</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.54369260617026</v>
+        <v>18.53048791765855</v>
       </c>
       <c r="C5" t="n">
-        <v>33.94392687433348</v>
+        <v>126.7436286182632</v>
       </c>
       <c r="D5" t="n">
-        <v>35.41654843070369</v>
+        <v>41.35612204139689</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.01386764104647</v>
+        <v>13.12203981496287</v>
       </c>
       <c r="C6" t="n">
-        <v>19.48180144307371</v>
+        <v>116.2870338203305</v>
       </c>
       <c r="D6" t="n">
-        <v>31.67805317293184</v>
+        <v>35.50196048097316</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.108434215823654</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>15.09142570968197</v>
+        <v>50.00531931581128</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>24.70077223884975</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>43.61021477034756</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063556815741327</v>
+        <v>17.30801767343372</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22084514757493</v>
+        <v>113.3675157609909</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297667611805995</v>
+        <v>4.327004418358431</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.993569734426777</v>
+        <v>1.121155878249857</v>
       </c>
       <c r="C2" t="n">
-        <v>8.08272884906399</v>
+        <v>13.10535010399067</v>
       </c>
       <c r="D2" t="n">
-        <v>34.69300037267379</v>
+        <v>33.46090700384404</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.52972715413255</v>
+        <v>4.255876297909923</v>
       </c>
       <c r="C3" t="n">
-        <v>37.3358651925062</v>
+        <v>24.69586350032851</v>
       </c>
       <c r="D3" t="n">
-        <v>63.96577167020094</v>
+        <v>74.642277953885</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.99988649347554</v>
+        <v>10.96317661332413</v>
       </c>
       <c r="C4" t="n">
-        <v>64.91119470939061</v>
+        <v>57.8789359038707</v>
       </c>
       <c r="D4" t="n">
-        <v>66.02155136289375</v>
+        <v>80.04778081346792</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.26299487821369</v>
+        <v>19.09499284760047</v>
       </c>
       <c r="C5" t="n">
-        <v>60.62292073724056</v>
+        <v>125.0255701358313</v>
       </c>
       <c r="D5" t="n">
-        <v>46.78027810736052</v>
+        <v>53.4070751110265</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.80131141531043</v>
+        <v>18.71701998146544</v>
       </c>
       <c r="C6" t="n">
-        <v>40.05039759474864</v>
+        <v>157.303471156058</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>39.60762938013333</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.87562114119692</v>
+        <v>11.25868267230242</v>
       </c>
       <c r="C7" t="n">
-        <v>22.93657161431823</v>
+        <v>105.4004335279376</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>39.04606969330414</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>19.86075605691297</v>
+        <v>43.81049130201391</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.287859095863181</v>
+        <v>17.6904196387419</v>
       </c>
       <c r="C21" t="n">
-        <v>75.6115381195805</v>
+        <v>126.4865004170046</v>
       </c>
       <c r="D21" t="n">
-        <v>6.376876708880283</v>
+        <v>5.307125891622571</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.560618996853934</v>
+        <v>1.048506548135594</v>
       </c>
       <c r="C2" t="n">
-        <v>5.080544369477244</v>
+        <v>8.282023633026093</v>
       </c>
       <c r="D2" t="n">
-        <v>34.12653194732337</v>
+        <v>26.66328589963912</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.09775816426395</v>
+        <v>6.454991155422778</v>
       </c>
       <c r="C3" t="n">
-        <v>33.76721228756904</v>
+        <v>42.62257657987527</v>
       </c>
       <c r="D3" t="n">
-        <v>76.8757539810465</v>
+        <v>81.04818172409543</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.4285503873329</v>
+        <v>9.163633071439728</v>
       </c>
       <c r="C4" t="n">
-        <v>81.77074803442109</v>
+        <v>97.41784294470675</v>
       </c>
       <c r="D4" t="n">
-        <v>83.26398629258047</v>
+        <v>72.45396232111885</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.83503499462009</v>
+        <v>10.52924412804704</v>
       </c>
       <c r="C5" t="n">
-        <v>93.90416791120742</v>
+        <v>93.97779898902593</v>
       </c>
       <c r="D5" t="n">
-        <v>59.51845456996289</v>
+        <v>39.04901493641689</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.99127174831558</v>
+        <v>6.963536466222627</v>
       </c>
       <c r="C6" t="n">
-        <v>71.48694083243576</v>
+        <v>69.39385472698156</v>
       </c>
       <c r="D6" t="n">
-        <v>42.9082651618111</v>
+        <v>25.68055644768807</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.69702517448201</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>42.27994663109313</v>
+        <v>30.78171751895449</v>
       </c>
       <c r="D7" t="n">
-        <v>36.71049190490098</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>25.95250056176443</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>24.62812290873548</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.498320129728268</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.29339147565905</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.498320129728268</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
